--- a/data/outputSpecialityRpt/File1/RPT_RPT5713512752455CZ_outputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/File1/RPT_RPT5713512752455CZ_outputSpecialityRpt.xlsx
@@ -853,75 +853,75 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>61958190101</t>
+          <t>NEWGENERICS50881000560</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>GENVOYA</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>HIV-MULTICLASS COMBO</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I15" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" s="14" t="n">
-        <v>3.269524076413061</v>
+        <v>0</v>
       </c>
       <c r="K15" s="14" t="n">
-        <v>3.413150240056282</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14" t="n">
-        <v>3.561892538059612</v>
+        <v>5.012533127775788</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>3.709127855005548</v>
+        <v>8.263025452994869</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>3.860116052895252</v>
+        <v>9.041561113907653</v>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>$45533.8798828125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>$53195.712724811725</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
         <is>
-          <t>$58647.740568944224</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R15" s="14" t="inlineStr">
         <is>
-          <t>$64609.366114305165</t>
+          <t>$106591.17160370485</t>
         </is>
       </c>
       <c r="S15" s="14" t="inlineStr">
         <is>
-          <t>$71008.47065235334</t>
+          <t>$177070.92585934117</t>
         </is>
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>$78017.84784231914</t>
+          <t>$195252.1286859344</t>
         </is>
       </c>
       <c r="U15" s="14" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>50881000560</t>
+          <t>61958190101</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>JAKAFI</t>
+          <t>GENVOYA</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-MULTICLASS COMBO</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1017,51 +1017,51 @@
         </is>
       </c>
       <c r="I16" s="14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J16" s="14" t="n">
-        <v>12.59985365085722</v>
+        <v>3.269524076413061</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>13.32162497706858</v>
+        <v>3.413150240056282</v>
       </c>
       <c r="L16" s="14" t="n">
-        <v>9.094389543047971</v>
+        <v>3.561892538059612</v>
       </c>
       <c r="M16" s="14" t="n">
-        <v>6.565167734083305</v>
+        <v>3.709127855005549</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>6.5647845446993</v>
+        <v>3.860116052895252</v>
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>$253440.0</t>
+          <t>$45533.8798828125</t>
         </is>
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>$293041.1658512486</t>
+          <t>$53195.71272481171</t>
         </is>
       </c>
       <c r="Q16" s="14" t="inlineStr">
         <is>
-          <t>$312203.80011073657</t>
+          <t>$58647.74056894421</t>
         </is>
       </c>
       <c r="R16" s="14" t="inlineStr">
         <is>
-          <t>$214677.92189651012</t>
+          <t>$64609.36611430518</t>
         </is>
       </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
-          <t>$156062.08516272577</t>
+          <t>$71008.47065235334</t>
         </is>
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>$157195.95483108654</t>
+          <t>$78017.84784231913</t>
         </is>
       </c>
       <c r="U16" s="14" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>00069068803</t>
+          <t>55513071001</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>IBRANCE</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1157,101 +1157,101 @@
         </is>
       </c>
       <c r="I17" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J17" s="14" t="n">
-        <v>3.34373388931461</v>
+        <v>1.087318936751969</v>
       </c>
       <c r="K17" s="14" t="n">
-        <v>2.162341945141449</v>
+        <v>1.116849987562997</v>
       </c>
       <c r="L17" s="14" t="n">
-        <v>2.153975914873203</v>
+        <v>1.153088422964832</v>
       </c>
       <c r="M17" s="14" t="n">
-        <v>2.246219480843963</v>
+        <v>1.178948229431164</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>2.369353439304804</v>
+        <v>1.204659816627253</v>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>$237052.796875</t>
+          <t>$2250.52001953125</t>
         </is>
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>$204556.77500006996</t>
+          <t>$2675.660353185906</t>
         </is>
       </c>
       <c r="Q17" s="14" t="inlineStr">
         <is>
-          <t>$135665.30437921124</t>
+          <t>$2943.901237394969</t>
         </is>
       </c>
       <c r="R17" s="14" t="inlineStr">
         <is>
-          <t>$138535.96138567786</t>
+          <t>$3246.58014127411</t>
         </is>
       </c>
       <c r="S17" s="14" t="inlineStr">
         <is>
-          <t>$148066.23352719384</t>
+          <t>$3537.4331219582064</t>
         </is>
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>$160120.674216525</t>
+          <t>$3853.181583567908</t>
         </is>
       </c>
       <c r="U17" s="14" t="inlineStr">
         <is>
-          <t>$153417.58125005246</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="V17" s="14" t="inlineStr">
         <is>
-          <t>$135665.30437921124</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="W17" s="14" t="inlineStr">
         <is>
-          <t>$138535.96138567786</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="X17" s="14" t="inlineStr">
         <is>
-          <t>$148066.23352719384</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Y17" s="14" t="inlineStr">
         <is>
-          <t>$160120.674216525</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Z17" s="14" t="inlineStr">
         <is>
-          <t>$103638.13432329954</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AA17" s="14" t="inlineStr">
         <is>
-          <t>$89361.6108545089</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AB17" s="14" t="inlineStr">
         <is>
-          <t>$89015.87370460626</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AC17" s="14" t="inlineStr">
         <is>
-          <t>$92827.95979239298</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="AD17" s="14" t="inlineStr">
         <is>
-          <t>$97916.6317777265</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>59676056201</t>
+          <t>00006022761</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>PREZISTA</t>
+          <t>ISENTRESS</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>HIV-PROTEASE INHIBITOR</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1300,48 +1300,48 @@
         <v>3</v>
       </c>
       <c r="J18" s="14" t="n">
-        <v>1.217192490284854</v>
+        <v>0.1283085548260666</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>1.215143212769734</v>
+        <v>0.04258839286573688</v>
       </c>
       <c r="L18" s="14" t="n">
-        <v>1.211712538387685</v>
+        <v>0.03870435936300515</v>
       </c>
       <c r="M18" s="14" t="n">
-        <v>1.204742038813293</v>
+        <v>0.03490022882701123</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>1.197088048792683</v>
+        <v>0.03145098360834659</v>
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>$23308.01953125</t>
+          <t>$22498.5615234375</t>
         </is>
       </c>
       <c r="P18" s="14" t="inlineStr">
         <is>
-          <t>$9999.367588661733</t>
+          <t>$1026.7935941429648</t>
         </is>
       </c>
       <c r="Q18" s="14" t="inlineStr">
         <is>
-          <t>$10441.694719497129</t>
+          <t>$357.6327106341913</t>
         </is>
       </c>
       <c r="R18" s="14" t="inlineStr">
         <is>
-          <t>$10888.04295797371</t>
+          <t>$340.13714912623055</t>
         </is>
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>$11338.972939974046</t>
+          <t>$320.1641443648764</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>$11805.020346401123</t>
+          <t>$301.27316273036837</t>
         </is>
       </c>
       <c r="U18" s="14" t="inlineStr">
@@ -1449,7 +1449,7 @@
         <v>0.8267626857316338</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>0.5968334303712095</v>
+        <v>0.5968334303712097</v>
       </c>
       <c r="N19" s="14" t="n">
         <v>0.5967985949726636</v>
@@ -1461,17 +1461,17 @@
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>$24420.09715427072</t>
+          <t>$24420.097154270712</t>
         </is>
       </c>
       <c r="Q19" s="14" t="inlineStr">
         <is>
-          <t>$26016.983342561383</t>
+          <t>$26016.98334256138</t>
         </is>
       </c>
       <c r="R19" s="14" t="inlineStr">
         <is>
-          <t>$17889.826824709173</t>
+          <t>$17889.826824709176</t>
         </is>
       </c>
       <c r="S19" s="14" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>$13099.662902590542</t>
+          <t>$13099.66290259054</t>
         </is>
       </c>
       <c r="U19" s="14" t="inlineStr">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>00006022761</t>
+          <t>NEWGENERICS49702022813</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>ISENTRESS</t>
+          <t>NEW GENERIC TIVICAY</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -1568,60 +1568,60 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I20" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" s="14" t="n">
-        <v>0.1283085548260666</v>
+        <v>0</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>0.04258839286573688</v>
+        <v>0.2679033920902113</v>
       </c>
       <c r="L20" s="14" t="n">
-        <v>0.03870435936300515</v>
+        <v>1.228456205077303</v>
       </c>
       <c r="M20" s="14" t="n">
-        <v>0.03490022882701122</v>
+        <v>1.2083195692084</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>0.03145098360834659</v>
+        <v>1.115228172138179</v>
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>$22498.5615234375</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P20" s="14" t="inlineStr">
         <is>
-          <t>$1026.793594142965</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q20" s="14" t="inlineStr">
         <is>
-          <t>$357.6327106341914</t>
+          <t>$772.6764577630839</t>
         </is>
       </c>
       <c r="R20" s="14" t="inlineStr">
         <is>
-          <t>$340.1371491262305</t>
+          <t>$3741.4591499830344</t>
         </is>
       </c>
       <c r="S20" s="14" t="inlineStr">
         <is>
-          <t>$320.1641443648764</t>
+          <t>$3869.4651350843787</t>
         </is>
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>$301.2731627303684</t>
+          <t>$3755.09267511723</t>
         </is>
       </c>
       <c r="U20" s="14" t="inlineStr">
@@ -1693,75 +1693,75 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>55513071021</t>
+          <t>NEWGENERICS00006022761</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>NEW GENERIC ISENTRESS</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I21" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" s="14" t="n">
-        <v>3.261956810255907</v>
+        <v>2.407514145417649</v>
       </c>
       <c r="K21" s="14" t="n">
-        <v>3.35054996268899</v>
+        <v>2.26648199863115</v>
       </c>
       <c r="L21" s="14" t="n">
-        <v>3.459265268894496</v>
+        <v>2.063276219719166</v>
       </c>
       <c r="M21" s="14" t="n">
-        <v>3.53684468829349</v>
+        <v>1.856256072233232</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>3.613979449881759</v>
+        <v>1.667472793610845</v>
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>$6751.56005859375</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P21" s="14" t="inlineStr">
         <is>
-          <t>$8090.394872082701</t>
+          <t>$17346.380019715285</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
         <is>
-          <t>$8725.103171649751</t>
+          <t>$17137.08960751975</t>
         </is>
       </c>
       <c r="R21" s="14" t="inlineStr">
         <is>
-          <t>$9454.015265212744</t>
+          <t>$16334.344338281517</t>
         </is>
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>$10142.179256673318</t>
+          <t>$15351.078574122137</t>
         </is>
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>$10877.156895780536</t>
+          <t>$14405.105306875577</t>
         </is>
       </c>
       <c r="U21" s="14" t="inlineStr">
@@ -1833,17 +1833,17 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00006022761</t>
+          <t>NEWGENERICS00069068803</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC ISENTRESS</t>
+          <t>NEW GENERIC IBRANCE</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1860,19 +1860,19 @@
         <v>0</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>2.407514145417649</v>
+        <v>1.223268386795488</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>2.26648199863115</v>
+        <v>2.640074959153961</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>2.063276219719166</v>
+        <v>2.959764318325942</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>1.856256072233232</v>
+        <v>3.143570417129168</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>1.667472793610845</v>
+        <v>3.305337151730743</v>
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
@@ -1881,27 +1881,27 @@
       </c>
       <c r="P22" s="14" t="inlineStr">
         <is>
-          <t>$17346.380019715285</t>
+          <t>$67377.73158159513</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr">
         <is>
-          <t>$17137.08960751975</t>
+          <t>$149141.83746188597</t>
         </is>
       </c>
       <c r="R22" s="14" t="inlineStr">
         <is>
-          <t>$16334.344338281517</t>
+          <t>$171486.11442726935</t>
         </is>
       </c>
       <c r="S22" s="14" t="inlineStr">
         <is>
-          <t>$15351.078574122135</t>
+          <t>$186802.90316288552</t>
         </is>
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>$14405.105306875581</t>
+          <t>$201448.8496683908</t>
         </is>
       </c>
       <c r="U22" s="14" t="inlineStr">
@@ -1973,75 +1973,75 @@
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>55513071001</t>
+          <t>NEWGENERICS50881001060</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>NEW GENERIC JAKAFI</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I23" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>1.087318936751969</v>
+        <v>0</v>
       </c>
       <c r="K23" s="14" t="n">
-        <v>1.116849987562997</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14" t="n">
-        <v>1.153088422964832</v>
+        <v>0.4556848297977988</v>
       </c>
       <c r="M23" s="14" t="n">
-        <v>1.178948229431164</v>
+        <v>0.7511841320904425</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>1.204659816627253</v>
+        <v>0.8219601012643319</v>
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>$2250.52001953125</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>$2675.6603531859064</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="Q23" s="14" t="inlineStr">
         <is>
-          <t>$2943.9012373949695</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="R23" s="14" t="inlineStr">
         <is>
-          <t>$3246.5801412741093</t>
+          <t>$8882.59763364207</t>
         </is>
       </c>
       <c r="S23" s="14" t="inlineStr">
         <is>
-          <t>$3537.4331219582064</t>
+          <t>$14755.910488278432</t>
         </is>
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>$3853.181583567909</t>
+          <t>$16271.010723827869</t>
         </is>
       </c>
       <c r="U23" s="14" t="inlineStr">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>49702022813</t>
+          <t>55513071021</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>TIVICAY</t>
+          <t>PROLIA</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -2137,51 +2137,51 @@
         </is>
       </c>
       <c r="I24" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>1.709918094502012</v>
+        <v>3.261956810255907</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>1.291163361090298</v>
+        <v>3.35054996268899</v>
       </c>
       <c r="L24" s="14" t="n">
-        <v>0.1749400441307497</v>
+        <v>3.459265268894496</v>
       </c>
       <c r="M24" s="14" t="n">
-        <v>0.05293065433551086</v>
+        <v>3.536844688293491</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>0.01731726103012906</v>
+        <v>3.613979449881759</v>
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>$5580.3798828125</t>
+          <t>$6751.56005859375</t>
         </is>
       </c>
       <c r="P24" s="14" t="inlineStr">
         <is>
-          <t>$5168.514808532099</t>
+          <t>$8090.394872082699</t>
         </is>
       </c>
       <c r="Q24" s="14" t="inlineStr">
         <is>
-          <t>$4135.822109656021</t>
+          <t>$8725.10317164975</t>
         </is>
       </c>
       <c r="R24" s="14" t="inlineStr">
         <is>
-          <t>$591.4532348453184</t>
+          <t>$9454.015265212745</t>
         </is>
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>$188.0268207855051</t>
+          <t>$10142.179256673318</t>
         </is>
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>$64.65537946872067</t>
+          <t>$10877.156895780534</t>
         </is>
       </c>
       <c r="U24" s="14" t="inlineStr">
@@ -2253,75 +2253,75 @@
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881001060</t>
+          <t>49702022813</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>TIVICAY</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>HIV-INTEGRASE INHIBITOR</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>0</v>
+        <v>1.709918094502012</v>
       </c>
       <c r="K25" s="14" t="n">
-        <v>0</v>
+        <v>1.291163361090298</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>0.4556848297977988</v>
+        <v>0.1749400441307497</v>
       </c>
       <c r="M25" s="14" t="n">
-        <v>0.7511841320904425</v>
+        <v>0.05293065433551088</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>0.8219601012643319</v>
+        <v>0.01731726103012906</v>
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5580.3798828125</t>
         </is>
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$5168.514808532098</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$4135.82210965602</t>
         </is>
       </c>
       <c r="R25" s="14" t="inlineStr">
         <is>
-          <t>$8882.59763364207</t>
+          <t>$591.4532348453185</t>
         </is>
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>$14755.91048827843</t>
+          <t>$188.0268207855051</t>
         </is>
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>$16271.010723827874</t>
+          <t>$64.65537946872065</t>
         </is>
       </c>
       <c r="U25" s="14" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="P26" s="14" t="inlineStr">
         <is>
-          <t>$95050.5962197075</t>
+          <t>$95050.59621970747</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
         <is>
-          <t>$99421.30528385166</t>
+          <t>$99421.30528385165</t>
         </is>
       </c>
       <c r="R26" s="14" t="inlineStr">
         <is>
-          <t>$104834.19392788445</t>
+          <t>$104834.19392788447</t>
         </is>
       </c>
       <c r="S26" s="14" t="inlineStr">
@@ -2461,22 +2461,22 @@
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>$114996.76032201329</t>
+          <t>$114996.76032201326</t>
         </is>
       </c>
       <c r="U26" s="14" t="inlineStr">
         <is>
-          <t>$95050.5962197075</t>
+          <t>$95050.59621970747</t>
         </is>
       </c>
       <c r="V26" s="14" t="inlineStr">
         <is>
-          <t>$99421.30528385166</t>
+          <t>$99421.30528385165</t>
         </is>
       </c>
       <c r="W26" s="14" t="inlineStr">
         <is>
-          <t>$104834.19392788445</t>
+          <t>$104834.19392788447</t>
         </is>
       </c>
       <c r="X26" s="14" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="Y26" s="14" t="inlineStr">
         <is>
-          <t>$114996.76032201329</t>
+          <t>$114996.76032201326</t>
         </is>
       </c>
       <c r="Z26" s="14" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="AC26" s="14" t="inlineStr">
         <is>
-          <t>$23550.31820528784</t>
+          <t>$23550.318205287844</t>
         </is>
       </c>
       <c r="AD26" s="14" t="inlineStr">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS49702022813</t>
+          <t>NEWGENERICS59676056201</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC TIVICAY</t>
+          <t>NEW GENERIC PREZISTA</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>HIV-INTEGRASE INHIBITOR</t>
+          <t>HIV-PROTEASE INHIBITOR</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -2560,19 +2560,19 @@
         <v>0</v>
       </c>
       <c r="J27" s="14" t="n">
-        <v>0</v>
+        <v>1.76125553811915</v>
       </c>
       <c r="K27" s="14" t="n">
-        <v>0.2679033920902113</v>
+        <v>1.751767324460131</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>1.228456205077303</v>
+        <v>1.749786351114981</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>1.2083195692084</v>
+        <v>1.735767735036898</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>1.115228172138179</v>
+        <v>1.719248099140247</v>
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
@@ -2581,27 +2581,27 @@
       </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$13027.110988077864</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
         <is>
-          <t>$772.6764577630839</t>
+          <t>$13553.727764667197</t>
         </is>
       </c>
       <c r="R27" s="14" t="inlineStr">
         <is>
-          <t>$3741.4591499830344</t>
+          <t>$14163.983046465342</t>
         </is>
       </c>
       <c r="S27" s="14" t="inlineStr">
         <is>
-          <t>$3869.4651350843783</t>
+          <t>$14727.460065934401</t>
         </is>
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>$3755.0926751172315</t>
+          <t>$15290.111912396334</t>
         </is>
       </c>
       <c r="U27" s="14" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS50881000560</t>
+          <t>00069068803</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC JAKAFI</t>
+          <t>IBRANCE</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2688,110 +2688,110 @@
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I28" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14" t="n">
-        <v>0</v>
+        <v>3.34373388931461</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>2.162341945141449</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>5.012533127775788</v>
+        <v>2.153975914873203</v>
       </c>
       <c r="M28" s="14" t="n">
-        <v>8.263025452994869</v>
+        <v>2.246219480843964</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>9.041561113907653</v>
+        <v>2.369353439304804</v>
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$237052.796875</t>
         </is>
       </c>
       <c r="P28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$204556.7750000699</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$135665.30437921121</t>
         </is>
       </c>
       <c r="R28" s="14" t="inlineStr">
         <is>
-          <t>$106591.17160370485</t>
+          <t>$138535.9613856779</t>
         </is>
       </c>
       <c r="S28" s="14" t="inlineStr">
         <is>
-          <t>$177070.92585934114</t>
+          <t>$148066.23352719384</t>
         </is>
       </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>$195252.12868593447</t>
+          <t>$160120.67421652496</t>
         </is>
       </c>
       <c r="U28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$153417.58125005243</t>
         </is>
       </c>
       <c r="V28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$135665.30437921121</t>
         </is>
       </c>
       <c r="W28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$138535.9613856779</t>
         </is>
       </c>
       <c r="X28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$148066.23352719384</t>
         </is>
       </c>
       <c r="Y28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$160120.67421652496</t>
         </is>
       </c>
       <c r="Z28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$103638.13432329954</t>
         </is>
       </c>
       <c r="AA28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$89361.6108545089</t>
         </is>
       </c>
       <c r="AB28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$89015.87370460626</t>
         </is>
       </c>
       <c r="AC28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$92827.959792393</t>
         </is>
       </c>
       <c r="AD28" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$97916.6317777265</t>
         </is>
       </c>
     </row>
@@ -2813,12 +2813,12 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS00069068803</t>
+          <t>50881000560</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC IBRANCE</t>
+          <t>JAKAFI</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -2828,60 +2828,60 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J29" s="14" t="n">
-        <v>1.223268386795488</v>
+        <v>12.59985365085722</v>
       </c>
       <c r="K29" s="14" t="n">
-        <v>2.640074959153961</v>
+        <v>13.32162497706858</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>2.959764318325942</v>
+        <v>9.094389543047971</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>3.143570417129168</v>
+        <v>6.565167734083307</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>3.305337151730743</v>
+        <v>6.5647845446993</v>
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$253440.0</t>
         </is>
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>$67377.73158159513</t>
+          <t>$293041.16585124854</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
         <is>
-          <t>$149141.83746188597</t>
+          <t>$312203.8001107365</t>
         </is>
       </c>
       <c r="R29" s="14" t="inlineStr">
         <is>
-          <t>$171486.11442726935</t>
+          <t>$214677.92189651018</t>
         </is>
       </c>
       <c r="S29" s="14" t="inlineStr">
         <is>
-          <t>$186802.9031628855</t>
+          <t>$156062.08516272577</t>
         </is>
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>$201448.84966839085</t>
+          <t>$157195.9548310865</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>NEWGENERICS59676056201</t>
+          <t>59676056201</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>NEW GENERIC PREZISTA</t>
+          <t>PREZISTA</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2968,60 +2968,60 @@
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I30" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14" t="n">
-        <v>1.76125553811915</v>
+        <v>1.217192490284854</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>1.751767324460131</v>
+        <v>1.215143212769734</v>
       </c>
       <c r="L30" s="14" t="n">
-        <v>1.749786351114981</v>
+        <v>1.211712538387685</v>
       </c>
       <c r="M30" s="14" t="n">
-        <v>1.735767735036898</v>
+        <v>1.204742038813293</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>1.719248099140247</v>
+        <v>1.197088048792683</v>
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$23308.01953125</t>
         </is>
       </c>
       <c r="P30" s="14" t="inlineStr">
         <is>
-          <t>$13027.110988077864</t>
+          <t>$9999.367588661731</t>
         </is>
       </c>
       <c r="Q30" s="14" t="inlineStr">
         <is>
-          <t>$13553.727764667197</t>
+          <t>$10441.694719497127</t>
         </is>
       </c>
       <c r="R30" s="14" t="inlineStr">
         <is>
-          <t>$14163.983046465342</t>
+          <t>$10888.042957973712</t>
         </is>
       </c>
       <c r="S30" s="14" t="inlineStr">
         <is>
-          <t>$14727.4600659344</t>
+          <t>$11338.972939974046</t>
         </is>
       </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>$15290.11191239634</t>
+          <t>$11805.02034640112</t>
         </is>
       </c>
       <c r="U30" s="14" t="inlineStr">
